--- a/utils/monday_sprint_sprint_2024-33.xlsx
+++ b/utils/monday_sprint_sprint_2024-33.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="574" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="574" uniqueCount="147">
   <si>
     <t>Ticket</t>
   </si>
@@ -42,7 +42,7 @@
     <t>Equipe TI</t>
   </si>
   <si>
-    <t>Entrada Sprint</t>
+    <t>Abertura</t>
   </si>
   <si>
     <t>Encerramento</t>
@@ -51,7 +51,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>SLA (15 dias)</t>
+    <t>Dentro da SLA</t>
   </si>
   <si>
     <t>Semana</t>
@@ -60,7 +60,7 @@
     <t>Mês</t>
   </si>
   <si>
-    <t>25326</t>
+    <t>6347368142</t>
   </si>
   <si>
     <t>Setor não informado</t>
@@ -87,7 +87,7 @@
     <t>28/03/2024</t>
   </si>
   <si>
-    <t>N/A</t>
+    <t>14/04/2024</t>
   </si>
   <si>
     <t>Feito</t>
@@ -102,7 +102,7 @@
     <t>Março</t>
   </si>
   <si>
-    <t>24746</t>
+    <t>6363989030</t>
   </si>
   <si>
     <t>Projeto</t>
@@ -123,16 +123,19 @@
     <t>Abril</t>
   </si>
   <si>
+    <t>6364036203</t>
+  </si>
+  <si>
     <t>AJUSTES CONDIÇÃO DE PAGAMENTO OFERTA / CPC - Consulta de Fluxo</t>
   </si>
   <si>
-    <t>24901</t>
+    <t>6363002230</t>
   </si>
   <si>
     <t>Sistema de Previsão de Vendas (Ofertas e Forecast)</t>
   </si>
   <si>
-    <t>22418</t>
+    <t>5209275005</t>
   </si>
   <si>
     <t>Melhorias Sistema de Apontamentos Moldagem ULE</t>
@@ -144,7 +147,7 @@
     <t>Setembro</t>
   </si>
   <si>
-    <t>23316</t>
+    <t>6269828396</t>
   </si>
   <si>
     <t>Desenvolver Consistência Apontamento de Horas - Ajustagem da Usinagem</t>
@@ -153,16 +156,22 @@
     <t>15/03/2024</t>
   </si>
   <si>
+    <t>13/04/2024</t>
+  </si>
+  <si>
     <t>Semana 3</t>
   </si>
   <si>
-    <t>25131</t>
+    <t>6269842245</t>
   </si>
   <si>
     <t>[ANALISE] Melhoria: criação tela MRP</t>
   </si>
   <si>
-    <t>6090</t>
+    <t>11/04/2024</t>
+  </si>
+  <si>
+    <t>6276838635</t>
   </si>
   <si>
     <t>Sistema Novo de Revisão de Documentos - Sprint FINAL</t>
@@ -171,7 +180,10 @@
     <t>18/03/2024</t>
   </si>
   <si>
-    <t>25175</t>
+    <t>31/03/2024</t>
+  </si>
+  <si>
+    <t>6291373856</t>
   </si>
   <si>
     <t>Dados Para Projeto Andon - Komatsu - Painel de gestão a vista</t>
@@ -180,7 +192,7 @@
     <t>19/03/2024</t>
   </si>
   <si>
-    <t>24556</t>
+    <t>6376153805</t>
   </si>
   <si>
     <t>Controle de Período Firme - Inconsistencias - Homologação</t>
@@ -189,7 +201,7 @@
     <t>02/04/2024</t>
   </si>
   <si>
-    <t>25356</t>
+    <t>6393959881</t>
   </si>
   <si>
     <t>QlikSense - campos</t>
@@ -198,7 +210,7 @@
     <t>04/04/2024</t>
   </si>
   <si>
-    <t>22015</t>
+    <t>6182744156</t>
   </si>
   <si>
     <t>Valorização e Movimentação dos Estoques de Produtos</t>
@@ -207,91 +219,100 @@
     <t>03/03/2024</t>
   </si>
   <si>
-    <t>25080</t>
+    <t>09/04/2024</t>
+  </si>
+  <si>
+    <t>6268841223</t>
   </si>
   <si>
     <t>Inventário de Item em Pré Lista</t>
   </si>
   <si>
-    <t>24903</t>
+    <t>6269062926</t>
   </si>
   <si>
     <t>Sistema de corridas</t>
   </si>
   <si>
-    <t>25346</t>
+    <t>6347291812</t>
   </si>
   <si>
     <t>Atualização Tela e Cabeçalho AP-119</t>
   </si>
   <si>
-    <t>25009</t>
+    <t>6347943967</t>
   </si>
   <si>
     <t>Apontamento de Inspeção (Máquinas)</t>
   </si>
   <si>
-    <t>25170</t>
+    <t>6347843942</t>
   </si>
   <si>
     <t>SISTEMA DE MOVIMENTAÇÃO DE SEQUÊNCIA - Criar rotina para e-mail desmoldagem</t>
   </si>
   <si>
-    <t>24975</t>
+    <t>6347998833</t>
   </si>
   <si>
     <t>Alçadas DHO</t>
   </si>
   <si>
-    <t>25336</t>
+    <t>6347323218</t>
   </si>
   <si>
     <t>Materiais Sem Saldo na Pre-Lista</t>
   </si>
   <si>
-    <t>25330</t>
+    <t>6347339140</t>
   </si>
   <si>
     <t>Altona || Sistema ERP || Estoque de Imobilizado X Patrimônio</t>
   </si>
   <si>
-    <t>25323</t>
+    <t>10/04/2024</t>
+  </si>
+  <si>
+    <t>6347383279</t>
   </si>
   <si>
     <t>Melhoria portal de pendencias</t>
   </si>
   <si>
-    <t>24962</t>
+    <t>6347977355</t>
   </si>
   <si>
     <t>Alçada Sr Cacídio</t>
   </si>
   <si>
-    <t>25328</t>
+    <t>6347354802</t>
   </si>
   <si>
     <t>Ajustes sistema de corridas</t>
   </si>
   <si>
-    <t>25331</t>
+    <t>6347333927</t>
   </si>
   <si>
     <t>Altona || Sistema ERP || PIS e Cofins sobre o Frete - Imobilizado</t>
   </si>
   <si>
-    <t>25280</t>
+    <t>6347473466</t>
   </si>
   <si>
     <t>Aviso para migração de OTF</t>
   </si>
   <si>
-    <t>25240</t>
+    <t>6347590222</t>
   </si>
   <si>
     <t>Sequência em aberto por setor.</t>
   </si>
   <si>
-    <t>25422</t>
+    <t>03/04/2024</t>
+  </si>
+  <si>
+    <t>6459448127</t>
   </si>
   <si>
     <t>Sistema de Custeio - REVISÃO Cálculo de Mão de Obra Fundição</t>
@@ -300,31 +321,34 @@
     <t>15/04/2024</t>
   </si>
   <si>
-    <t>25480</t>
+    <t>6459464307</t>
   </si>
   <si>
     <t>Sistema de Custeio - Valorização e Movimentação dos Estoques de Produtos</t>
   </si>
   <si>
-    <t>25154</t>
+    <t>6347893494</t>
   </si>
   <si>
     <t>Documentos Anexos - Certificados - FQA - Ficha de Qualidade Altona</t>
   </si>
   <si>
-    <t>25178</t>
+    <t>6347678300</t>
   </si>
   <si>
     <t>Lançamento de notas - totalizador da NF</t>
   </si>
   <si>
-    <t>25351</t>
+    <t>6348373663</t>
   </si>
   <si>
     <t>Sistema de modelos - histórico de conserto</t>
   </si>
   <si>
-    <t>25349</t>
+    <t>07/04/2024</t>
+  </si>
+  <si>
+    <t>6349641950</t>
   </si>
   <si>
     <t>Campo "WCPP23" - OTF dos Conjuntos</t>
@@ -336,7 +360,7 @@
     <t>Período</t>
   </si>
   <si>
-    <t>SPRINT 2024-33</t>
+    <t>Set/2023</t>
   </si>
   <si>
     <t>Base</t>
@@ -396,10 +420,16 @@
     <t>A fazer</t>
   </si>
   <si>
+    <t>Semana 2</t>
+  </si>
+  <si>
     <t>Abertos</t>
   </si>
   <si>
     <t>Impedimento</t>
+  </si>
+  <si>
+    <t>Semana 5</t>
   </si>
   <si>
     <t>Baixa</t>
@@ -1001,7 +1031,7 @@
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>16</v>
@@ -1013,10 +1043,10 @@
         <v>18</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>32</v>
@@ -1048,7 +1078,7 @@
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>16</v>
@@ -1060,10 +1090,10 @@
         <v>18</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>32</v>
@@ -1095,7 +1125,7 @@
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>16</v>
@@ -1107,10 +1137,10 @@
         <v>18</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>32</v>
@@ -1122,7 +1152,7 @@
         <v>22</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K6" s="2" t="s">
         <v>24</v>
@@ -1137,12 +1167,12 @@
         <v>27</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>16</v>
@@ -1154,10 +1184,10 @@
         <v>18</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>20</v>
@@ -1169,10 +1199,10 @@
         <v>22</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>24</v>
+        <v>47</v>
       </c>
       <c r="L7" s="2" t="s">
         <v>25</v>
@@ -1181,7 +1211,7 @@
         <v>26</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="O7" s="2" t="s">
         <v>28</v>
@@ -1189,7 +1219,7 @@
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>16</v>
@@ -1201,10 +1231,10 @@
         <v>18</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>20</v>
@@ -1216,10 +1246,10 @@
         <v>22</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>24</v>
+        <v>51</v>
       </c>
       <c r="L8" s="2" t="s">
         <v>25</v>
@@ -1228,7 +1258,7 @@
         <v>26</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="O8" s="2" t="s">
         <v>28</v>
@@ -1236,7 +1266,7 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>16</v>
@@ -1248,10 +1278,10 @@
         <v>18</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>20</v>
@@ -1263,10 +1293,10 @@
         <v>22</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>24</v>
+        <v>55</v>
       </c>
       <c r="L9" s="2" t="s">
         <v>25</v>
@@ -1275,7 +1305,7 @@
         <v>26</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="O9" s="2" t="s">
         <v>28</v>
@@ -1283,7 +1313,7 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>16</v>
@@ -1295,10 +1325,10 @@
         <v>18</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>20</v>
@@ -1310,10 +1340,10 @@
         <v>22</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>24</v>
+        <v>55</v>
       </c>
       <c r="L10" s="2" t="s">
         <v>25</v>
@@ -1322,7 +1352,7 @@
         <v>26</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="O10" s="2" t="s">
         <v>28</v>
@@ -1330,7 +1360,7 @@
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>16</v>
@@ -1342,10 +1372,10 @@
         <v>18</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>32</v>
@@ -1357,10 +1387,10 @@
         <v>22</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="L11" s="2" t="s">
         <v>25</v>
@@ -1377,7 +1407,7 @@
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>16</v>
@@ -1389,10 +1419,10 @@
         <v>18</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>20</v>
@@ -1404,10 +1434,10 @@
         <v>22</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>24</v>
+        <v>64</v>
       </c>
       <c r="L12" s="2" t="s">
         <v>25</v>
@@ -1424,7 +1454,7 @@
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>16</v>
@@ -1436,10 +1466,10 @@
         <v>18</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>20</v>
@@ -1451,10 +1481,10 @@
         <v>22</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
       <c r="L13" s="2" t="s">
         <v>25</v>
@@ -1471,7 +1501,7 @@
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>16</v>
@@ -1483,10 +1513,10 @@
         <v>18</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>20</v>
@@ -1498,10 +1528,10 @@
         <v>22</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>24</v>
+        <v>55</v>
       </c>
       <c r="L14" s="2" t="s">
         <v>25</v>
@@ -1510,7 +1540,7 @@
         <v>26</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="O14" s="2" t="s">
         <v>28</v>
@@ -1518,7 +1548,7 @@
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>16</v>
@@ -1530,10 +1560,10 @@
         <v>18</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>20</v>
@@ -1545,10 +1575,10 @@
         <v>22</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>24</v>
+        <v>55</v>
       </c>
       <c r="L15" s="2" t="s">
         <v>25</v>
@@ -1557,7 +1587,7 @@
         <v>26</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="O15" s="2" t="s">
         <v>28</v>
@@ -1565,7 +1595,7 @@
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>16</v>
@@ -1577,10 +1607,10 @@
         <v>18</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>20</v>
@@ -1595,7 +1625,7 @@
         <v>23</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>24</v>
+        <v>47</v>
       </c>
       <c r="L16" s="2" t="s">
         <v>25</v>
@@ -1612,7 +1642,7 @@
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>16</v>
@@ -1624,10 +1654,10 @@
         <v>18</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>20</v>
@@ -1642,7 +1672,7 @@
         <v>23</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>24</v>
+        <v>51</v>
       </c>
       <c r="L17" s="2" t="s">
         <v>25</v>
@@ -1659,7 +1689,7 @@
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>16</v>
@@ -1671,10 +1701,10 @@
         <v>18</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>20</v>
@@ -1689,7 +1719,7 @@
         <v>23</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>24</v>
+        <v>47</v>
       </c>
       <c r="L18" s="2" t="s">
         <v>25</v>
@@ -1706,7 +1736,7 @@
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>16</v>
@@ -1718,10 +1748,10 @@
         <v>18</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>20</v>
@@ -1736,7 +1766,7 @@
         <v>23</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>24</v>
+        <v>55</v>
       </c>
       <c r="L19" s="2" t="s">
         <v>25</v>
@@ -1753,7 +1783,7 @@
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>16</v>
@@ -1765,10 +1795,10 @@
         <v>18</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>20</v>
@@ -1783,7 +1813,7 @@
         <v>23</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>24</v>
+        <v>61</v>
       </c>
       <c r="L20" s="2" t="s">
         <v>25</v>
@@ -1800,7 +1830,7 @@
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>16</v>
@@ -1812,10 +1842,10 @@
         <v>18</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>20</v>
@@ -1830,7 +1860,7 @@
         <v>23</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>24</v>
+        <v>85</v>
       </c>
       <c r="L21" s="2" t="s">
         <v>25</v>
@@ -1847,7 +1877,7 @@
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>16</v>
@@ -1859,10 +1889,10 @@
         <v>18</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>20</v>
@@ -1877,7 +1907,7 @@
         <v>23</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>24</v>
+        <v>55</v>
       </c>
       <c r="L22" s="2" t="s">
         <v>25</v>
@@ -1894,7 +1924,7 @@
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>16</v>
@@ -1906,10 +1936,10 @@
         <v>18</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>20</v>
@@ -1924,7 +1954,7 @@
         <v>23</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>24</v>
+        <v>55</v>
       </c>
       <c r="L23" s="2" t="s">
         <v>25</v>
@@ -1941,7 +1971,7 @@
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>16</v>
@@ -1953,10 +1983,10 @@
         <v>18</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>20</v>
@@ -1971,7 +2001,7 @@
         <v>23</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>24</v>
+        <v>51</v>
       </c>
       <c r="L24" s="2" t="s">
         <v>25</v>
@@ -1988,7 +2018,7 @@
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>16</v>
@@ -2000,10 +2030,10 @@
         <v>18</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>20</v>
@@ -2018,7 +2048,7 @@
         <v>23</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>24</v>
+        <v>51</v>
       </c>
       <c r="L25" s="2" t="s">
         <v>25</v>
@@ -2035,7 +2065,7 @@
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>16</v>
@@ -2047,10 +2077,10 @@
         <v>18</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>20</v>
@@ -2065,7 +2095,7 @@
         <v>23</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>24</v>
+        <v>47</v>
       </c>
       <c r="L26" s="2" t="s">
         <v>25</v>
@@ -2082,7 +2112,7 @@
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>16</v>
@@ -2094,10 +2124,10 @@
         <v>18</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>20</v>
@@ -2112,7 +2142,7 @@
         <v>23</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>24</v>
+        <v>98</v>
       </c>
       <c r="L27" s="2" t="s">
         <v>25</v>
@@ -2129,7 +2159,7 @@
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>16</v>
@@ -2141,10 +2171,10 @@
         <v>18</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>32</v>
@@ -2156,7 +2186,7 @@
         <v>22</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="K28" s="2" t="s">
         <v>24</v>
@@ -2168,7 +2198,7 @@
         <v>26</v>
       </c>
       <c r="N28" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="O28" s="2" t="s">
         <v>35</v>
@@ -2176,7 +2206,7 @@
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>16</v>
@@ -2188,10 +2218,10 @@
         <v>18</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>32</v>
@@ -2203,7 +2233,7 @@
         <v>22</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="K29" s="2" t="s">
         <v>24</v>
@@ -2215,7 +2245,7 @@
         <v>26</v>
       </c>
       <c r="N29" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="O29" s="2" t="s">
         <v>35</v>
@@ -2223,7 +2253,7 @@
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>16</v>
@@ -2235,10 +2265,10 @@
         <v>18</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>20</v>
@@ -2253,7 +2283,7 @@
         <v>23</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>24</v>
+        <v>47</v>
       </c>
       <c r="L30" s="2" t="s">
         <v>25</v>
@@ -2270,7 +2300,7 @@
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>16</v>
@@ -2282,10 +2312,10 @@
         <v>18</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>20</v>
@@ -2300,7 +2330,7 @@
         <v>23</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>24</v>
+        <v>85</v>
       </c>
       <c r="L31" s="2" t="s">
         <v>25</v>
@@ -2317,7 +2347,7 @@
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>16</v>
@@ -2329,10 +2359,10 @@
         <v>18</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>20</v>
@@ -2347,7 +2377,7 @@
         <v>23</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>24</v>
+        <v>110</v>
       </c>
       <c r="L32" s="2" t="s">
         <v>25</v>
@@ -2364,7 +2394,7 @@
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>16</v>
@@ -2376,10 +2406,10 @@
         <v>18</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="G33" s="2" t="s">
         <v>20</v>
@@ -2394,7 +2424,7 @@
         <v>23</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>24</v>
+        <v>98</v>
       </c>
       <c r="L33" s="2" t="s">
         <v>25</v>
@@ -2422,23 +2452,23 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="B2" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="D2" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="E2" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="F2"/>
       <c r="G2"/>
@@ -2446,16 +2476,16 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -2466,7 +2496,7 @@
         <v>0</v>
       </c>
       <c r="G5" s="4">
-        <v>0</v>
+        <v>18.97</v>
       </c>
       <c r="J5" s="4">
         <v>1</v>
@@ -2474,7 +2504,7 @@
     </row>
     <row r="21" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J21" s="6" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
     </row>
     <row r="22" spans="10:11" x14ac:dyDescent="0.25">
@@ -2487,7 +2517,7 @@
     </row>
     <row r="23" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J23" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="K23">
         <v>0</v>
@@ -2495,7 +2525,7 @@
     </row>
     <row r="24" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J24" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="K24">
         <v>0</v>
@@ -2526,12 +2556,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="B2">
         <v>32</v>
@@ -2545,7 +2575,7 @@
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>0</v>
+        <v>18.97</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
@@ -2555,25 +2585,25 @@
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>6</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="M9" s="6" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="P9" s="6" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="Q9" s="6" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
@@ -2590,13 +2620,13 @@
         <v>28</v>
       </c>
       <c r="G10" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="H10">
         <v>0</v>
       </c>
       <c r="J10" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="K10">
         <v>0</v>
@@ -2634,16 +2664,16 @@
         <v>32</v>
       </c>
       <c r="M11" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="N11">
         <v>0</v>
       </c>
       <c r="P11" t="s">
-        <v>46</v>
+        <v>135</v>
       </c>
       <c r="Q11">
-        <v>8</v>
+        <v>19</v>
       </c>
     </row>
     <row r="12" spans="7:17" x14ac:dyDescent="0.25">
@@ -2654,33 +2684,33 @@
         <v>25</v>
       </c>
       <c r="J12" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="K12">
         <v>0</v>
       </c>
       <c r="M12" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="N12">
         <v>0</v>
       </c>
       <c r="P12" t="s">
-        <v>27</v>
+        <v>138</v>
       </c>
       <c r="Q12">
-        <v>18</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G13" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="H13">
         <v>0</v>
       </c>
       <c r="M13" t="s">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="N13">
         <v>0</v>
@@ -2688,13 +2718,13 @@
     </row>
     <row r="14" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G14" t="s">
-        <v>131</v>
+        <v>141</v>
       </c>
       <c r="H14">
         <v>0</v>
       </c>
       <c r="M14" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="N14">
         <v>0</v>
@@ -2702,7 +2732,7 @@
     </row>
     <row r="15" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M15" t="s">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="N15">
         <v>0</v>
@@ -2710,7 +2740,7 @@
     </row>
     <row r="16" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M16" t="s">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="N16">
         <v>0</v>
@@ -2718,7 +2748,7 @@
     </row>
     <row r="17" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M17" t="s">
-        <v>134</v>
+        <v>144</v>
       </c>
       <c r="N17">
         <v>0</v>
@@ -2726,10 +2756,10 @@
     </row>
     <row r="19" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D19" s="6" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="20" ht="18" customHeight="1" spans="4:7" x14ac:dyDescent="0.25">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="20" spans="4:7" x14ac:dyDescent="0.25">
       <c r="D20" s="1" t="s">
         <v>0</v>
       </c>
@@ -2737,7 +2767,7 @@
         <v>1</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>4</v>
@@ -2751,7 +2781,7 @@
         <v>16</v>
       </c>
       <c r="F21" s="2">
-        <v>0</v>
+        <v>192</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>19</v>
@@ -2765,7 +2795,7 @@
         <v>16</v>
       </c>
       <c r="F22" s="2">
-        <v>0</v>
+        <v>192</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>31</v>
@@ -2773,114 +2803,114 @@
     </row>
     <row r="23" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D23" s="2" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F23" s="2">
-        <v>0</v>
+        <v>192</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="24" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D24" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F24" s="2">
-        <v>0</v>
+        <v>192</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="25" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D25" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F25" s="2">
-        <v>0</v>
+        <v>192</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="26" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D26" s="2" t="s">
-        <v>43</v>
+        <v>99</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F26" s="2">
-        <v>0</v>
+        <v>192</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>44</v>
+        <v>100</v>
       </c>
     </row>
     <row r="27" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D27" s="2" t="s">
-        <v>47</v>
+        <v>102</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F27" s="2">
-        <v>0</v>
+        <v>192</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>48</v>
+        <v>103</v>
       </c>
     </row>
     <row r="28" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D28" s="2" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F28" s="2">
-        <v>0</v>
+        <v>191</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
     </row>
     <row r="29" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D29" s="2" t="s">
-        <v>52</v>
+        <v>73</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F29" s="2">
-        <v>0</v>
+        <v>191</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>53</v>
+        <v>74</v>
       </c>
     </row>
     <row r="30" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D30" s="2" t="s">
-        <v>55</v>
+        <v>77</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F30" s="2">
-        <v>0</v>
+        <v>191</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>56</v>
+        <v>78</v>
       </c>
     </row>
   </sheetData>
